--- a/137556_Cuenca_Chillon/_raw_reportes_xlsx/IDConfig_64959_completo.xlsx
+++ b/137556_Cuenca_Chillon/_raw_reportes_xlsx/IDConfig_64959_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rdf9e7dc342934296"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R3f341711f7f34bce"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4809</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2173</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2742</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9472</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5806</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7817</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8545</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6677</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7817</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/137556_Cuenca_Chillon/_raw_reportes_xlsx/IDConfig_64959_completo.xlsx
+++ b/137556_Cuenca_Chillon/_raw_reportes_xlsx/IDConfig_64959_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R3f341711f7f34bce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rdea8dd9402dd4ea5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3554</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3143</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0242</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0491</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2212</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2509</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7780</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7191</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6766</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3621</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1405</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2445</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5537</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8851</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1990</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8995</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4754</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5273</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4876</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.2649</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9686</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.2215</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9989</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7325</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7884</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3464</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1527</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.2313</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0358</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3931</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4553</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3190</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9560</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5011</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3647</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6544</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1972</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3893</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3962</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2742</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1061</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0811</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7338</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5843</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6861</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8303</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
